--- a/lib/plantillas-aseguradoras/sbs.xlsx
+++ b/lib/plantillas-aseguradoras/sbs.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Hoja3" sheetId="4" r:id="rId4" state="hidden"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template endosos financieros'!A2:AE22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template endosos financieros'!A2:AE62</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -919,8 +919,888 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="K23">
+        <f>+I23*J23</f>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f>+K23*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M23" t="str" cm="1">
+        <f t="array" ref="M23">IFS(H23&gt;L23,"No puede expedirse, No cumple con el parámetro",H23&lt;1,"Ups! Aún no diligencias la columna H",H23&lt;=L23,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IF(M23="No puede expedirse, No cumple con el parámetro",K23*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O23" t="str" cm="1">
+        <f t="array" ref="O23">IFS(N23=0,"",H23&gt;N23,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H23&lt;1,"Ups! Aún no diligencias la columna H",H23&lt;=N23,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="K24">
+        <f>+I24*J24</f>
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <f>+K24*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M24" t="str" cm="1">
+        <f t="array" ref="M24">IFS(H24&gt;L24,"No puede expedirse, No cumple con el parámetro",H24&lt;1,"Ups! Aún no diligencias la columna H",H24&lt;=L24,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IF(M24="No puede expedirse, No cumple con el parámetro",K24*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" t="str" cm="1">
+        <f t="array" ref="O24">IFS(N24=0,"",H24&gt;N24,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H24&lt;1,"Ups! Aún no diligencias la columna H",H24&lt;=N24,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="K25">
+        <f>+I25*J25</f>
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <f>+K25*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M25" t="str" cm="1">
+        <f t="array" ref="M25">IFS(H25&gt;L25,"No puede expedirse, No cumple con el parámetro",H25&lt;1,"Ups! Aún no diligencias la columna H",H25&lt;=L25,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IF(M25="No puede expedirse, No cumple con el parámetro",K25*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" t="str" cm="1">
+        <f t="array" ref="O25">IFS(N25=0,"",H25&gt;N25,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H25&lt;1,"Ups! Aún no diligencias la columna H",H25&lt;=N25,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="K26">
+        <f>+I26*J26</f>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f>+K26*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M26" t="str" cm="1">
+        <f t="array" ref="M26">IFS(H26&gt;L26,"No puede expedirse, No cumple con el parámetro",H26&lt;1,"Ups! Aún no diligencias la columna H",H26&lt;=L26,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IF(M26="No puede expedirse, No cumple con el parámetro",K26*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" t="str" cm="1">
+        <f t="array" ref="O26">IFS(N26=0,"",H26&gt;N26,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H26&lt;1,"Ups! Aún no diligencias la columna H",H26&lt;=N26,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="K27">
+        <f>+I27*J27</f>
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <f>+K27*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M27" t="str" cm="1">
+        <f t="array" ref="M27">IFS(H27&gt;L27,"No puede expedirse, No cumple con el parámetro",H27&lt;1,"Ups! Aún no diligencias la columna H",H27&lt;=L27,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IF(M27="No puede expedirse, No cumple con el parámetro",K27*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" t="str" cm="1">
+        <f t="array" ref="O27">IFS(N27=0,"",H27&gt;N27,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H27&lt;1,"Ups! Aún no diligencias la columna H",H27&lt;=N27,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="K28">
+        <f>+I28*J28</f>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f>+K28*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M28" t="str" cm="1">
+        <f t="array" ref="M28">IFS(H28&gt;L28,"No puede expedirse, No cumple con el parámetro",H28&lt;1,"Ups! Aún no diligencias la columna H",H28&lt;=L28,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IF(M28="No puede expedirse, No cumple con el parámetro",K28*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" t="str" cm="1">
+        <f t="array" ref="O28">IFS(N28=0,"",H28&gt;N28,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H28&lt;1,"Ups! Aún no diligencias la columna H",H28&lt;=N28,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="K29">
+        <f>+I29*J29</f>
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <f>+K29*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M29" t="str" cm="1">
+        <f t="array" ref="M29">IFS(H29&gt;L29,"No puede expedirse, No cumple con el parámetro",H29&lt;1,"Ups! Aún no diligencias la columna H",H29&lt;=L29,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IF(M29="No puede expedirse, No cumple con el parámetro",K29*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" t="str" cm="1">
+        <f t="array" ref="O29">IFS(N29=0,"",H29&gt;N29,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H29&lt;1,"Ups! Aún no diligencias la columna H",H29&lt;=N29,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="K30">
+        <f>+I30*J30</f>
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <f>+K30*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M30" t="str" cm="1">
+        <f t="array" ref="M30">IFS(H30&gt;L30,"No puede expedirse, No cumple con el parámetro",H30&lt;1,"Ups! Aún no diligencias la columna H",H30&lt;=L30,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IF(M30="No puede expedirse, No cumple con el parámetro",K30*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" t="str" cm="1">
+        <f t="array" ref="O30">IFS(N30=0,"",H30&gt;N30,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H30&lt;1,"Ups! Aún no diligencias la columna H",H30&lt;=N30,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="K31">
+        <f>+I31*J31</f>
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <f>+K31*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M31" t="str" cm="1">
+        <f t="array" ref="M31">IFS(H31&gt;L31,"No puede expedirse, No cumple con el parámetro",H31&lt;1,"Ups! Aún no diligencias la columna H",H31&lt;=L31,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IF(M31="No puede expedirse, No cumple con el parámetro",K31*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" t="str" cm="1">
+        <f t="array" ref="O31">IFS(N31=0,"",H31&gt;N31,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H31&lt;1,"Ups! Aún no diligencias la columna H",H31&lt;=N31,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="K32">
+        <f>+I32*J32</f>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f>+K32*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M32" t="str" cm="1">
+        <f t="array" ref="M32">IFS(H32&gt;L32,"No puede expedirse, No cumple con el parámetro",H32&lt;1,"Ups! Aún no diligencias la columna H",H32&lt;=L32,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IF(M32="No puede expedirse, No cumple con el parámetro",K32*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O32" t="str" cm="1">
+        <f t="array" ref="O32">IFS(N32=0,"",H32&gt;N32,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H32&lt;1,"Ups! Aún no diligencias la columna H",H32&lt;=N32,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33">
+        <f>+I33*J33</f>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f>+K33*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M33" t="str" cm="1">
+        <f t="array" ref="M33">IFS(H33&gt;L33,"No puede expedirse, No cumple con el parámetro",H33&lt;1,"Ups! Aún no diligencias la columna H",H33&lt;=L33,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IF(M33="No puede expedirse, No cumple con el parámetro",K33*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O33" t="str" cm="1">
+        <f t="array" ref="O33">IFS(N33=0,"",H33&gt;N33,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H33&lt;1,"Ups! Aún no diligencias la columna H",H33&lt;=N33,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="K34">
+        <f>+I34*J34</f>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f>+K34*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M34" t="str" cm="1">
+        <f t="array" ref="M34">IFS(H34&gt;L34,"No puede expedirse, No cumple con el parámetro",H34&lt;1,"Ups! Aún no diligencias la columna H",H34&lt;=L34,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IF(M34="No puede expedirse, No cumple con el parámetro",K34*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" t="str" cm="1">
+        <f t="array" ref="O34">IFS(N34=0,"",H34&gt;N34,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H34&lt;1,"Ups! Aún no diligencias la columna H",H34&lt;=N34,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="K35">
+        <f>+I35*J35</f>
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <f>+K35*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M35" t="str" cm="1">
+        <f t="array" ref="M35">IFS(H35&gt;L35,"No puede expedirse, No cumple con el parámetro",H35&lt;1,"Ups! Aún no diligencias la columna H",H35&lt;=L35,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IF(M35="No puede expedirse, No cumple con el parámetro",K35*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O35" t="str" cm="1">
+        <f t="array" ref="O35">IFS(N35=0,"",H35&gt;N35,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H35&lt;1,"Ups! Aún no diligencias la columna H",H35&lt;=N35,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="K36">
+        <f>+I36*J36</f>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <f>+K36*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M36" t="str" cm="1">
+        <f t="array" ref="M36">IFS(H36&gt;L36,"No puede expedirse, No cumple con el parámetro",H36&lt;1,"Ups! Aún no diligencias la columna H",H36&lt;=L36,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IF(M36="No puede expedirse, No cumple con el parámetro",K36*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O36" t="str" cm="1">
+        <f t="array" ref="O36">IFS(N36=0,"",H36&gt;N36,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H36&lt;1,"Ups! Aún no diligencias la columna H",H36&lt;=N36,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="K37">
+        <f>+I37*J37</f>
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <f>+K37*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M37" t="str" cm="1">
+        <f t="array" ref="M37">IFS(H37&gt;L37,"No puede expedirse, No cumple con el parámetro",H37&lt;1,"Ups! Aún no diligencias la columna H",H37&lt;=L37,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IF(M37="No puede expedirse, No cumple con el parámetro",K37*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O37" t="str" cm="1">
+        <f t="array" ref="O37">IFS(N37=0,"",H37&gt;N37,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H37&lt;1,"Ups! Aún no diligencias la columna H",H37&lt;=N37,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="K38">
+        <f>+I38*J38</f>
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <f>+K38*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M38" t="str" cm="1">
+        <f t="array" ref="M38">IFS(H38&gt;L38,"No puede expedirse, No cumple con el parámetro",H38&lt;1,"Ups! Aún no diligencias la columna H",H38&lt;=L38,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IF(M38="No puede expedirse, No cumple con el parámetro",K38*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O38" t="str" cm="1">
+        <f t="array" ref="O38">IFS(N38=0,"",H38&gt;N38,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H38&lt;1,"Ups! Aún no diligencias la columna H",H38&lt;=N38,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="K39">
+        <f>+I39*J39</f>
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <f>+K39*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M39" t="str" cm="1">
+        <f t="array" ref="M39">IFS(H39&gt;L39,"No puede expedirse, No cumple con el parámetro",H39&lt;1,"Ups! Aún no diligencias la columna H",H39&lt;=L39,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IF(M39="No puede expedirse, No cumple con el parámetro",K39*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O39" t="str" cm="1">
+        <f t="array" ref="O39">IFS(N39=0,"",H39&gt;N39,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H39&lt;1,"Ups! Aún no diligencias la columna H",H39&lt;=N39,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="K40">
+        <f>+I40*J40</f>
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <f>+K40*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M40" t="str" cm="1">
+        <f t="array" ref="M40">IFS(H40&gt;L40,"No puede expedirse, No cumple con el parámetro",H40&lt;1,"Ups! Aún no diligencias la columna H",H40&lt;=L40,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IF(M40="No puede expedirse, No cumple con el parámetro",K40*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O40" t="str" cm="1">
+        <f t="array" ref="O40">IFS(N40=0,"",H40&gt;N40,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H40&lt;1,"Ups! Aún no diligencias la columna H",H40&lt;=N40,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="K41">
+        <f>+I41*J41</f>
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <f>+K41*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M41" t="str" cm="1">
+        <f t="array" ref="M41">IFS(H41&gt;L41,"No puede expedirse, No cumple con el parámetro",H41&lt;1,"Ups! Aún no diligencias la columna H",H41&lt;=L41,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IF(M41="No puede expedirse, No cumple con el parámetro",K41*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O41" t="str" cm="1">
+        <f t="array" ref="O41">IFS(N41=0,"",H41&gt;N41,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H41&lt;1,"Ups! Aún no diligencias la columna H",H41&lt;=N41,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="K42">
+        <f>+I42*J42</f>
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <f>+K42*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M42" t="str" cm="1">
+        <f t="array" ref="M42">IFS(H42&gt;L42,"No puede expedirse, No cumple con el parámetro",H42&lt;1,"Ups! Aún no diligencias la columna H",H42&lt;=L42,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IF(M42="No puede expedirse, No cumple con el parámetro",K42*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O42" t="str" cm="1">
+        <f t="array" ref="O42">IFS(N42=0,"",H42&gt;N42,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H42&lt;1,"Ups! Aún no diligencias la columna H",H42&lt;=N42,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="K43">
+        <f>+I43*J43</f>
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <f>+K43*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M43" t="str" cm="1">
+        <f t="array" ref="M43">IFS(H43&gt;L43,"No puede expedirse, No cumple con el parámetro",H43&lt;1,"Ups! Aún no diligencias la columna H",H43&lt;=L43,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IF(M43="No puede expedirse, No cumple con el parámetro",K43*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O43" t="str" cm="1">
+        <f t="array" ref="O43">IFS(N43=0,"",H43&gt;N43,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H43&lt;1,"Ups! Aún no diligencias la columna H",H43&lt;=N43,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="K44">
+        <f>+I44*J44</f>
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <f>+K44*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M44" t="str" cm="1">
+        <f t="array" ref="M44">IFS(H44&gt;L44,"No puede expedirse, No cumple con el parámetro",H44&lt;1,"Ups! Aún no diligencias la columna H",H44&lt;=L44,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>IF(M44="No puede expedirse, No cumple con el parámetro",K44*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O44" t="str" cm="1">
+        <f t="array" ref="O44">IFS(N44=0,"",H44&gt;N44,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H44&lt;1,"Ups! Aún no diligencias la columna H",H44&lt;=N44,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="K45">
+        <f>+I45*J45</f>
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <f>+K45*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M45" t="str" cm="1">
+        <f t="array" ref="M45">IFS(H45&gt;L45,"No puede expedirse, No cumple con el parámetro",H45&lt;1,"Ups! Aún no diligencias la columna H",H45&lt;=L45,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>IF(M45="No puede expedirse, No cumple con el parámetro",K45*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O45" t="str" cm="1">
+        <f t="array" ref="O45">IFS(N45=0,"",H45&gt;N45,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H45&lt;1,"Ups! Aún no diligencias la columna H",H45&lt;=N45,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="K46">
+        <f>+I46*J46</f>
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <f>+K46*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M46" t="str" cm="1">
+        <f t="array" ref="M46">IFS(H46&gt;L46,"No puede expedirse, No cumple con el parámetro",H46&lt;1,"Ups! Aún no diligencias la columna H",H46&lt;=L46,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>IF(M46="No puede expedirse, No cumple con el parámetro",K46*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O46" t="str" cm="1">
+        <f t="array" ref="O46">IFS(N46=0,"",H46&gt;N46,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H46&lt;1,"Ups! Aún no diligencias la columna H",H46&lt;=N46,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="K47">
+        <f>+I47*J47</f>
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <f>+K47*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M47" t="str" cm="1">
+        <f t="array" ref="M47">IFS(H47&gt;L47,"No puede expedirse, No cumple con el parámetro",H47&lt;1,"Ups! Aún no diligencias la columna H",H47&lt;=L47,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>IF(M47="No puede expedirse, No cumple con el parámetro",K47*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O47" t="str" cm="1">
+        <f t="array" ref="O47">IFS(N47=0,"",H47&gt;N47,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H47&lt;1,"Ups! Aún no diligencias la columna H",H47&lt;=N47,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="K48">
+        <f>+I48*J48</f>
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <f>+K48*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M48" t="str" cm="1">
+        <f t="array" ref="M48">IFS(H48&gt;L48,"No puede expedirse, No cumple con el parámetro",H48&lt;1,"Ups! Aún no diligencias la columna H",H48&lt;=L48,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>IF(M48="No puede expedirse, No cumple con el parámetro",K48*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O48" t="str" cm="1">
+        <f t="array" ref="O48">IFS(N48=0,"",H48&gt;N48,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H48&lt;1,"Ups! Aún no diligencias la columna H",H48&lt;=N48,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="K49">
+        <f>+I49*J49</f>
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <f>+K49*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M49" t="str" cm="1">
+        <f t="array" ref="M49">IFS(H49&gt;L49,"No puede expedirse, No cumple con el parámetro",H49&lt;1,"Ups! Aún no diligencias la columna H",H49&lt;=L49,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>IF(M49="No puede expedirse, No cumple con el parámetro",K49*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O49" t="str" cm="1">
+        <f t="array" ref="O49">IFS(N49=0,"",H49&gt;N49,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H49&lt;1,"Ups! Aún no diligencias la columna H",H49&lt;=N49,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="K50">
+        <f>+I50*J50</f>
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <f>+K50*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M50" t="str" cm="1">
+        <f t="array" ref="M50">IFS(H50&gt;L50,"No puede expedirse, No cumple con el parámetro",H50&lt;1,"Ups! Aún no diligencias la columna H",H50&lt;=L50,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>IF(M50="No puede expedirse, No cumple con el parámetro",K50*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O50" t="str" cm="1">
+        <f t="array" ref="O50">IFS(N50=0,"",H50&gt;N50,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H50&lt;1,"Ups! Aún no diligencias la columna H",H50&lt;=N50,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="K51">
+        <f>+I51*J51</f>
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <f>+K51*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M51" t="str" cm="1">
+        <f t="array" ref="M51">IFS(H51&gt;L51,"No puede expedirse, No cumple con el parámetro",H51&lt;1,"Ups! Aún no diligencias la columna H",H51&lt;=L51,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>IF(M51="No puede expedirse, No cumple con el parámetro",K51*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O51" t="str" cm="1">
+        <f t="array" ref="O51">IFS(N51=0,"",H51&gt;N51,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H51&lt;1,"Ups! Aún no diligencias la columna H",H51&lt;=N51,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52">
+        <f>+I52*J52</f>
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <f>+K52*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M52" t="str" cm="1">
+        <f t="array" ref="M52">IFS(H52&gt;L52,"No puede expedirse, No cumple con el parámetro",H52&lt;1,"Ups! Aún no diligencias la columna H",H52&lt;=L52,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N52">
+        <f>IF(M52="No puede expedirse, No cumple con el parámetro",K52*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O52" t="str" cm="1">
+        <f t="array" ref="O52">IFS(N52=0,"",H52&gt;N52,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H52&lt;1,"Ups! Aún no diligencias la columna H",H52&lt;=N52,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="K53">
+        <f>+I53*J53</f>
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <f>+K53*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M53" t="str" cm="1">
+        <f t="array" ref="M53">IFS(H53&gt;L53,"No puede expedirse, No cumple con el parámetro",H53&lt;1,"Ups! Aún no diligencias la columna H",H53&lt;=L53,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>IF(M53="No puede expedirse, No cumple con el parámetro",K53*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O53" t="str" cm="1">
+        <f t="array" ref="O53">IFS(N53=0,"",H53&gt;N53,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H53&lt;1,"Ups! Aún no diligencias la columna H",H53&lt;=N53,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="K54">
+        <f>+I54*J54</f>
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <f>+K54*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M54" t="str" cm="1">
+        <f t="array" ref="M54">IFS(H54&gt;L54,"No puede expedirse, No cumple con el parámetro",H54&lt;1,"Ups! Aún no diligencias la columna H",H54&lt;=L54,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N54">
+        <f>IF(M54="No puede expedirse, No cumple con el parámetro",K54*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O54" t="str" cm="1">
+        <f t="array" ref="O54">IFS(N54=0,"",H54&gt;N54,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H54&lt;1,"Ups! Aún no diligencias la columna H",H54&lt;=N54,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55">
+        <f>+I55*J55</f>
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <f>+K55*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M55" t="str" cm="1">
+        <f t="array" ref="M55">IFS(H55&gt;L55,"No puede expedirse, No cumple con el parámetro",H55&lt;1,"Ups! Aún no diligencias la columna H",H55&lt;=L55,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N55">
+        <f>IF(M55="No puede expedirse, No cumple con el parámetro",K55*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O55" t="str" cm="1">
+        <f t="array" ref="O55">IFS(N55=0,"",H55&gt;N55,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H55&lt;1,"Ups! Aún no diligencias la columna H",H55&lt;=N55,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56">
+        <f>+I56*J56</f>
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <f>+K56*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M56" t="str" cm="1">
+        <f t="array" ref="M56">IFS(H56&gt;L56,"No puede expedirse, No cumple con el parámetro",H56&lt;1,"Ups! Aún no diligencias la columna H",H56&lt;=L56,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>IF(M56="No puede expedirse, No cumple con el parámetro",K56*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O56" t="str" cm="1">
+        <f t="array" ref="O56">IFS(N56=0,"",H56&gt;N56,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H56&lt;1,"Ups! Aún no diligencias la columna H",H56&lt;=N56,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57">
+        <f>+I57*J57</f>
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <f>+K57*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M57" t="str" cm="1">
+        <f t="array" ref="M57">IFS(H57&gt;L57,"No puede expedirse, No cumple con el parámetro",H57&lt;1,"Ups! Aún no diligencias la columna H",H57&lt;=L57,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF(M57="No puede expedirse, No cumple con el parámetro",K57*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O57" t="str" cm="1">
+        <f t="array" ref="O57">IFS(N57=0,"",H57&gt;N57,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H57&lt;1,"Ups! Aún no diligencias la columna H",H57&lt;=N57,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58">
+        <f>+I58*J58</f>
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <f>+K58*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M58" t="str" cm="1">
+        <f t="array" ref="M58">IFS(H58&gt;L58,"No puede expedirse, No cumple con el parámetro",H58&lt;1,"Ups! Aún no diligencias la columna H",H58&lt;=L58,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF(M58="No puede expedirse, No cumple con el parámetro",K58*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O58" t="str" cm="1">
+        <f t="array" ref="O58">IFS(N58=0,"",H58&gt;N58,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H58&lt;1,"Ups! Aún no diligencias la columna H",H58&lt;=N58,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59">
+        <f>+I59*J59</f>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f>+K59*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M59" t="str" cm="1">
+        <f t="array" ref="M59">IFS(H59&gt;L59,"No puede expedirse, No cumple con el parámetro",H59&lt;1,"Ups! Aún no diligencias la columna H",H59&lt;=L59,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IF(M59="No puede expedirse, No cumple con el parámetro",K59*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O59" t="str" cm="1">
+        <f t="array" ref="O59">IFS(N59=0,"",H59&gt;N59,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H59&lt;1,"Ups! Aún no diligencias la columna H",H59&lt;=N59,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60">
+        <f>+I60*J60</f>
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <f>+K60*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M60" t="str" cm="1">
+        <f t="array" ref="M60">IFS(H60&gt;L60,"No puede expedirse, No cumple con el parámetro",H60&lt;1,"Ups! Aún no diligencias la columna H",H60&lt;=L60,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>IF(M60="No puede expedirse, No cumple con el parámetro",K60*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O60" t="str" cm="1">
+        <f t="array" ref="O60">IFS(N60=0,"",H60&gt;N60,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H60&lt;1,"Ups! Aún no diligencias la columna H",H60&lt;=N60,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61">
+        <f>+I61*J61</f>
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <f>+K61*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M61" t="str" cm="1">
+        <f t="array" ref="M61">IFS(H61&gt;L61,"No puede expedirse, No cumple con el parámetro",H61&lt;1,"Ups! Aún no diligencias la columna H",H61&lt;=L61,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>IF(M61="No puede expedirse, No cumple con el parámetro",K61*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O61" t="str" cm="1">
+        <f t="array" ref="O61">IFS(N61=0,"",H61&gt;N61,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H61&lt;1,"Ups! Aún no diligencias la columna H",H61&lt;=N61,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62">
+        <f>+I62*J62</f>
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <f>+K62*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="M62" t="str" cm="1">
+        <f t="array" ref="M62">IFS(H62&gt;L62,"No puede expedirse, No cumple con el parámetro",H62&lt;1,"Ups! Aún no diligencias la columna H",H62&lt;=L62,"Adelante!, cumple con el parámetro")</f>
+        <v/>
+      </c>
+      <c r="N62">
+        <f>IF(M62="No puede expedirse, No cumple con el parámetro",K62*1.4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O62" t="str" cm="1">
+        <f t="array" ref="O62">IFS(N62=0,"",H62&gt;N62,"No puede expedirse, No cumple con el parámetro. Debes enviar correo a Heller con justificación",H62&lt;1,"Ups! Aún no diligencias la columna H",H62&lt;=N62,"Adelante!, cumple con el parámetro, debes enviar correo a Natalia")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AE22"/>
+  <autoFilter ref="A2:AE62"/>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -928,7 +1808,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/lib/plantillas-aseguradoras/sbs.xlsx
+++ b/lib/plantillas-aseguradoras/sbs.xlsx
@@ -38,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -46,7 +46,6 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
   <fonts count="1">
     <font>
